--- a/data/trending_integrated_20261026_10.xlsx
+++ b/data/trending_integrated_20261026_10.xlsx
@@ -578,13 +578,13 @@
         <v>-0.34</v>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="F2" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G2" t="n">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -610,7 +610,7 @@
         <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>58001582485</v>
+        <v>58130046535</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>루닛, 글로벌 AI 신약 밸류체인 합류 및 빅파마와 후기 임상 진입 등 구체적 사업 협력 뉴스. 공매도 관련 언급.</t>
+          <t>AI 신약 밸류체인 합류 및 빅파마와 협력 발표. 공매도 상환 압박 및 단기 급등 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI 신약', '글로벌 협력', '공매도']</t>
+          <t>['AI 신약', '빅파마 협력', '공매도']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5590</v>
+        <v>5680</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+1.82%</t>
+          <t>'+3.46%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G3" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -702,7 +702,7 @@
         <v>2.67</v>
       </c>
       <c r="O3" t="n">
-        <v>14769295105</v>
+        <v>15209447555</v>
       </c>
       <c r="P3" t="n">
         <v>7400</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>진양산업, 정치 테마 관련 부정적 언급과 함께 주가 하락 가능성 제기. 명확한 근거 없는 추측성 발언 다수.</t>
+          <t>정치 테마주에 대한 불신 및 하락 가능성 경고. 실체 없는 사기 주식으로 판단.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['정치 테마', '주가 하락']</t>
+          <t>['정치 테마주', '하락', '사기 주식']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1292000</v>
+        <v>1282500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.17%</t>
+          <t>'+0.43%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -765,10 +765,10 @@
         <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="G4" t="n">
-        <v>2015</v>
+        <v>1749</v>
       </c>
       <c r="H4" t="n">
         <v>48.69</v>
@@ -794,7 +794,7 @@
         <v>48.77</v>
       </c>
       <c r="O4" t="n">
-        <v>1012256361500</v>
+        <v>1073602387500</v>
       </c>
       <c r="P4" t="n">
         <v>2987000</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>SK하이닉스, 키옥시아 지분 차익 기반 16조원 특별배당 추진 등 구체적인 호재 언급. 나스닥 선물 급등 및 반도체 섹터 강세 전망.</t>
+          <t>16조 특별배당 및 AI 실적 전망에 따른 기대감. 나스닥 선물 폭등 및 단기 급등 가능성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['특별배당', '키옥시아', '반도체']</t>
+          <t>['특별배당', 'AI 실적', '나스닥 선물']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>214500</v>
+        <v>213000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-0.46%</t>
+          <t>'-1.16%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>758</v>
+        <v>790</v>
       </c>
       <c r="F5" t="n">
-        <v>436</v>
+        <v>454</v>
       </c>
       <c r="G5" t="n">
-        <v>1810</v>
+        <v>1912</v>
       </c>
       <c r="H5" t="n">
         <v>46.11</v>
@@ -886,7 +886,7 @@
         <v>46.13</v>
       </c>
       <c r="O5" t="n">
-        <v>799244337000</v>
+        <v>840341106750</v>
       </c>
       <c r="P5" t="n">
         <v>374500</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>삼성전자, 정치 테마 연관성 및 부정적 시장 전망 제기. 3분기 영업이익 호재 언급 있으나, 전반적 하락세 전망.</t>
+          <t>정치적 리스크 언급 및 3분기 영업이익 호재 기대. 기술적 분석 및 시장 하락 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['정치 테마', '시장 전망', '영업이익']</t>
+          <t>['기술적 분석', '영업이익', '시장 하락']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58400</v>
+        <v>58200</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-2.34%</t>
+          <t>'-2.68%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>1.49</v>
       </c>
       <c r="E6" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F6" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G6" t="n">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H6" t="n">
         <v>40.39</v>
@@ -972,13 +972,13 @@
         <v>60200</v>
       </c>
       <c r="M6" t="n">
-        <v>57800</v>
+        <v>57700</v>
       </c>
       <c r="N6" t="n">
         <v>38.9</v>
       </c>
       <c r="O6" t="n">
-        <v>108310452300</v>
+        <v>118314445450</v>
       </c>
       <c r="P6" t="n">
         <v>67300</v>
@@ -994,12 +994,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성E&amp;A, 대형 수주 공시 임박 및 외인/자사주 매수세 유입에 따른 상승 기대감. 중동 전쟁 관련 불확실성 존재.</t>
+          <t>본격적인 호재 시작 및 대형 수주 공시 임박 기대. 외인 및 자사주 매수세 유입 확인.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>57800</v>
+        <v>14240</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-2.69%</t>
+          <t>'-3.13%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.02</v>
+        <v>0.14</v>
       </c>
       <c r="E7" t="n">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="F7" t="n">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="G7" t="n">
-        <v>249</v>
+        <v>83</v>
       </c>
       <c r="H7" t="n">
-        <v>22.23</v>
+        <v>10.03</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,38 +1055,38 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>59400</v>
+        <v>14700</v>
       </c>
       <c r="K7" t="n">
-        <v>58300</v>
+        <v>14370</v>
       </c>
       <c r="L7" t="n">
-        <v>59100</v>
+        <v>14770</v>
       </c>
       <c r="M7" t="n">
-        <v>57600</v>
+        <v>14200</v>
       </c>
       <c r="N7" t="n">
-        <v>22.25</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>25311569200</v>
+        <v>10613503525</v>
       </c>
       <c r="P7" t="n">
-        <v>139200</v>
+        <v>40350</v>
       </c>
       <c r="Q7" t="n">
-        <v>57000</v>
+        <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>-1000</v>
+        <v>80000</v>
       </c>
       <c r="S7" t="n">
-        <v>-63000</v>
+        <v>-15000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>두산에너빌리티, 정치적 요인 및 시장 전반의 하락세 속에서 주가 하락 우려 제기. 신용 물량 및 IMF 관련 부정적 언급.</t>
+          <t>주가 조작 의혹 및 뱅크런 가능성 제기. 공매도 세력에 대한 비판 및 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['정치적 요인', '주가 하락', '신용 물량']</t>
+          <t>['주가 조작', '뱅크런', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14300</v>
+        <v>57500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.72%</t>
+          <t>'-3.20%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.14</v>
+        <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="F8" t="n">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="G8" t="n">
-        <v>76</v>
+        <v>280</v>
       </c>
       <c r="H8" t="n">
-        <v>10.03</v>
+        <v>22.23</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14700</v>
+        <v>59400</v>
       </c>
       <c r="K8" t="n">
-        <v>14370</v>
+        <v>58300</v>
       </c>
       <c r="L8" t="n">
-        <v>14770</v>
+        <v>59100</v>
       </c>
       <c r="M8" t="n">
-        <v>14250</v>
+        <v>57200</v>
       </c>
       <c r="N8" t="n">
-        <v>9.890000000000001</v>
+        <v>22.25</v>
       </c>
       <c r="O8" t="n">
-        <v>9664373770</v>
+        <v>28997053650</v>
       </c>
       <c r="P8" t="n">
-        <v>40350</v>
+        <v>139200</v>
       </c>
       <c r="Q8" t="n">
-        <v>3320</v>
+        <v>57000</v>
       </c>
       <c r="R8" t="n">
-        <v>80000</v>
+        <v>-1000</v>
       </c>
       <c r="S8" t="n">
-        <v>-15000</v>
+        <v>-63000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>대우건설, 정치적 요인 및 주가 조작 의혹 등 부정적 내용 중심. 명확한 사실 기반 분석 부재, 감정적 표현 다수.</t>
+          <t>회사 망한 것 아니냐는 의문 제기 및 주가 폭락 우려. 정치적 이슈와 연관된 주가 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['정치적 요인', '주가 조작', '감정적 표현']</t>
+          <t>['주가 하락', '정치 이슈', '회사 망함']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3310</v>
+        <v>3350</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-13.12%</t>
+          <t>'-12.07%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F9" t="n">
         <v>90</v>
       </c>
       <c r="G9" t="n">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1254,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>14222082940</v>
+        <v>14827264817</v>
       </c>
       <c r="P9" t="n">
         <v>7050</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>북한 군사 도발 관련 지정학적 리스크 부각. 주가 하락세 속에서 외국인 매수 기대감.</t>
+          <t>북한 관련 지정학적 리스크 언급 및 변동성 확대 예상. 차트 기반 단기 반등 가능성 및 외인 매수 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['지정학적 리스크', '북한 도발', '외국인 매수']</t>
+          <t>['지정학적 리스크', '차트 분석', '외인 매수']</t>
         </is>
       </c>
       <c r="X9" t="n">

--- a/data/trending_integrated_20261026_10.xlsx
+++ b/data/trending_integrated_20261026_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-0.34</v>
       </c>
       <c r="E2" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G2" t="n">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -610,7 +610,7 @@
         <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>58130046535</v>
+        <v>58252135125</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 신약 밸류체인 합류 및 빅파마와 협력 발표. 공매도 상환 압박 및 단기 급등 전망.</t>
+          <t>글로벌 AI 신약 밸류체인 합류 및 빅파마와 후기 임상 진입, 美 서밋과 항암 신약 개발 협력 등 구체적인 호재 언급. 공매도 상환 기대와 함께 급등 가능성 제시.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI 신약', '빅파마 협력', '공매도']</t>
+          <t>['AI 신약', '후기 임상', '항암 신약']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5680</v>
+        <v>5920</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+3.46%</t>
+          <t>'+7.83%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G3" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -702,7 +702,7 @@
         <v>2.67</v>
       </c>
       <c r="O3" t="n">
-        <v>15209447555</v>
+        <v>19140110395</v>
       </c>
       <c r="P3" t="n">
         <v>7400</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정치 테마주에 대한 불신 및 하락 가능성 경고. 실체 없는 사기 주식으로 판단.</t>
+          <t>오세훈 관련 정치 테마주로 언급. 지지율 상승 기대와 함께 사기 정치 테마 및 묻어두면 골로 간다는 부정적 전망 교차.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['정치 테마주', '하락', '사기 주식']</t>
+          <t>['정치 테마주', '지지율', '사기']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1282500</v>
+        <v>1294000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+0.43%</t>
+          <t>'+1.33%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -765,10 +765,10 @@
         <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="G4" t="n">
-        <v>1749</v>
+        <v>1551</v>
       </c>
       <c r="H4" t="n">
         <v>48.69</v>
@@ -794,7 +794,7 @@
         <v>48.77</v>
       </c>
       <c r="O4" t="n">
-        <v>1073602387500</v>
+        <v>1165818412500</v>
       </c>
       <c r="P4" t="n">
         <v>2987000</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>16조 특별배당 및 AI 실적 전망에 따른 기대감. 나스닥 선물 폭등 및 단기 급등 가능성 언급.</t>
+          <t>특별 배당 16조 지급 언급과 함께 폭락 및 하락 추세 가능성 제기. 외인 매수 부재 시 상승 불가 및 동시호가 장난질 신호 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['특별배당', 'AI 실적', '나스닥 선물']</t>
+          <t>['특별 배당', '하락 추세', '외인 매수']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>213000</v>
+        <v>214000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-1.16%</t>
+          <t>'-0.70%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>790</v>
+        <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="G5" t="n">
-        <v>1912</v>
+        <v>1795</v>
       </c>
       <c r="H5" t="n">
         <v>46.11</v>
@@ -886,7 +886,7 @@
         <v>46.13</v>
       </c>
       <c r="O5" t="n">
-        <v>840341106750</v>
+        <v>904437935250</v>
       </c>
       <c r="P5" t="n">
         <v>374500</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정치적 리스크 언급 및 3분기 영업이익 호재 기대. 기술적 분석 및 시장 하락 전망.</t>
+          <t>이재명 및 더불어민주당 리스크, 3분기 영업이익 호재 언급. 기술적 분석 및 나스닥 선물 폭등을 바탕으로 한 긍정적 기대와 함께 시스템 문제 및 폭락 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['기술적 분석', '영업이익', '시장 하락']</t>
+          <t>['기술적 분석', '영업이익', '시스템 문제']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58200</v>
+        <v>58600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-2.68%</t>
+          <t>'-2.01%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>1.49</v>
       </c>
       <c r="E6" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="F6" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G6" t="n">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="H6" t="n">
         <v>40.39</v>
@@ -978,7 +978,7 @@
         <v>38.9</v>
       </c>
       <c r="O6" t="n">
-        <v>118314445450</v>
+        <v>124657399650</v>
       </c>
       <c r="P6" t="n">
         <v>67300</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>본격적인 호재 시작 및 대형 수주 공시 임박 기대. 외인 및 자사주 매수세 유입 확인.</t>
+          <t>본격적인 호재 시작 전이며, 1000억대 매수 가능성 언급. 대형 수주 공시 임박 및 외인 공격적 매수세를 근거로 긍정적 전망 제시.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['대형 수주', '외인 매수', '자사주']</t>
+          <t>['대형 수주', '공시 임박', '외인 매수']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14240</v>
+        <v>16450</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-3.13%</t>
+          <t>'-2.26%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
       <c r="E7" t="n">
         <v>45</v>
       </c>
       <c r="F7" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G7" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H7" t="n">
-        <v>10.03</v>
+        <v>27.94</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>14700</v>
+        <v>16830</v>
       </c>
       <c r="K7" t="n">
-        <v>14370</v>
+        <v>16520</v>
       </c>
       <c r="L7" t="n">
-        <v>14770</v>
+        <v>16820</v>
       </c>
       <c r="M7" t="n">
-        <v>14200</v>
+        <v>16400</v>
       </c>
       <c r="N7" t="n">
-        <v>9.890000000000001</v>
+        <v>27.89</v>
       </c>
       <c r="O7" t="n">
-        <v>10613503525</v>
+        <v>11301294575</v>
       </c>
       <c r="P7" t="n">
-        <v>40350</v>
+        <v>35350</v>
       </c>
       <c r="Q7" t="n">
-        <v>3320</v>
+        <v>16400</v>
       </c>
       <c r="R7" t="n">
-        <v>80000</v>
+        <v>117000</v>
       </c>
       <c r="S7" t="n">
-        <v>-15000</v>
+        <v>-13000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>주가 조작 의혹 및 뱅크런 가능성 제기. 공매도 세력에 대한 비판 및 주가 하락 우려.</t>
+          <t>경제 위기 및 30000원 붕괴 가능성 언급. 과거 경영진 비판과 함께 중국 선박 수주 쏠림으로 인한 한국 조선 탈락 뉴스 인용. 투자가 밑 빠진 독에 물 붓기 같다고 평가.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['주가 조작', '뱅크런', '공매도']</t>
+          <t>['경제 위기', '선박 수주', '밑 빠진 독']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>57500</v>
+        <v>57600</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-3.20%</t>
+          <t>'-3.03%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F8" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G8" t="n">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="H8" t="n">
         <v>22.23</v>
@@ -1162,7 +1162,7 @@
         <v>22.25</v>
       </c>
       <c r="O8" t="n">
-        <v>28997053650</v>
+        <v>31044801050</v>
       </c>
       <c r="P8" t="n">
         <v>139200</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>회사 망한 것 아니냐는 의문 제기 및 주가 폭락 우려. 정치적 이슈와 연관된 주가 하락 가능성 언급.</t>
+          <t>회사 망한 거 아니냐는 부정적 평가와 함께 두산 묻은 종목 불매 선언. 주식시장 붕괴 및 IMF 가능성 언급. 현재 가격이 저점이라는 반론도 존재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['주가 하락', '정치 이슈', '회사 망함']</t>
+          <t>['주식시장 붕괴', 'IMF', '저점']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,70 +1207,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>빅텍</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3350</v>
+        <v>14240</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-12.07%</t>
+          <t>'-3.13%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="E9" t="n">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="F9" t="n">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="G9" t="n">
-        <v>197</v>
+        <v>86</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>10.03</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>3810</v>
+        <v>14700</v>
       </c>
       <c r="K9" t="n">
-        <v>3250</v>
+        <v>14370</v>
       </c>
       <c r="L9" t="n">
-        <v>3555</v>
+        <v>14770</v>
       </c>
       <c r="M9" t="n">
-        <v>3215</v>
+        <v>14190</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>14827264817</v>
+        <v>11677835580</v>
       </c>
       <c r="P9" t="n">
-        <v>7050</v>
+        <v>40350</v>
       </c>
       <c r="Q9" t="n">
-        <v>2500</v>
+        <v>3320</v>
       </c>
       <c r="R9" t="n">
-        <v>173000</v>
+        <v>80000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-15000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>북한 관련 지정학적 리스크 언급 및 변동성 확대 예상. 차트 기반 단기 반등 가능성 및 외인 매수 기대.</t>
+          <t>이재명 대통령 관련 정치적 언급과 함께 주가 조작, 뱅크런, 마진콜 등 부정적 용어 사용. 건설주 종전/휴전 기대와 실적 나오는 날 공매도 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,18 +1279,202 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['지정학적 리스크', '차트 분석', '외인 매수']</t>
+          <t>['주가 조작', '뱅크런', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>한화솔루션</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>26900</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>'-5.45%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E10" t="n">
+        <v>44</v>
+      </c>
+      <c r="F10" t="n">
+        <v>33</v>
+      </c>
+      <c r="G10" t="n">
+        <v>160</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>28450</v>
+      </c>
+      <c r="K10" t="n">
+        <v>27900</v>
+      </c>
+      <c r="L10" t="n">
+        <v>28200</v>
+      </c>
+      <c r="M10" t="n">
+        <v>26850</v>
+      </c>
+      <c r="N10" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="O10" t="n">
+        <v>23878287575</v>
+      </c>
+      <c r="P10" t="n">
+        <v>59300</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>22000</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-134000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-16000</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>혐오스럽고 만나기 싫은 종목으로 평가. 한국 압박 뉴스 언급 및 방송 후 하락, 거품 논란 제기. 2.7 저점 이탈 시 폭락 우려.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>['청정에너지', '거품', '폭락']</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>009830</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>빅텍</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3300</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>'-13.39%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>142</v>
+      </c>
+      <c r="F11" t="n">
+        <v>89</v>
+      </c>
+      <c r="G11" t="n">
+        <v>196</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>3810</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3250</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3555</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3215</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>15492475858</v>
+      </c>
+      <c r="P11" t="n">
+        <v>7050</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2500</v>
+      </c>
+      <c r="R11" t="n">
+        <v>173000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>북한 관련 지정학적 리스크(자주포, 전면전 위기) 언급. 미 선물 폭등 및 외인 매수 가능성 제기. 하락 후 말아올릴 가능성 언급.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['지정학적 리스크', '미 선물', '자주포']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
         <v>5</v>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>065450</t>
         </is>

--- a/data/trending_integrated_20261026_10.xlsx
+++ b/data/trending_integrated_20261026_10.xlsx
@@ -578,13 +578,13 @@
         <v>-0.34</v>
       </c>
       <c r="E2" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F2" t="n">
         <v>80</v>
       </c>
       <c r="G2" t="n">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -610,7 +610,7 @@
         <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>58252135125</v>
+        <v>58314729215</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>글로벌 AI 신약 밸류체인 합류 및 빅파마와 후기 임상 진입, 美 서밋과 항암 신약 개발 협력 등 구체적인 호재 언급. 공매도 상환 기대와 함께 급등 가능성 제시.</t>
+          <t>글로벌 AI 신약 밸류체인 합류 및 빅파마와의 협력에 따른 급등 및 장기 성장 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI 신약', '후기 임상', '항암 신약']</t>
+          <t>['AI 신약', '빅파마 협력', '급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5920</v>
+        <v>5800</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+7.83%</t>
+          <t>'+5.65%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G3" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -702,7 +702,7 @@
         <v>2.67</v>
       </c>
       <c r="O3" t="n">
-        <v>19140110395</v>
+        <v>22222281295</v>
       </c>
       <c r="P3" t="n">
         <v>7400</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>오세훈 관련 정치 테마주로 언급. 지지율 상승 기대와 함께 사기 정치 테마 및 묻어두면 골로 간다는 부정적 전망 교차.</t>
+          <t>정치 테마주로서의 실체 없는 기대감에 대한 비판 및 급락 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['정치 테마주', '지지율', '사기']</t>
+          <t>['정치 테마주', '실체 없음', '급락']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1294000</v>
+        <v>1299000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.33%</t>
+          <t>'+1.72%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -765,10 +765,10 @@
         <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="G4" t="n">
-        <v>1551</v>
+        <v>1499</v>
       </c>
       <c r="H4" t="n">
         <v>48.69</v>
@@ -794,7 +794,7 @@
         <v>48.77</v>
       </c>
       <c r="O4" t="n">
-        <v>1165818412500</v>
+        <v>1292385439000</v>
       </c>
       <c r="P4" t="n">
         <v>2987000</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>특별 배당 16조 지급 언급과 함께 폭락 및 하락 추세 가능성 제기. 외인 매수 부재 시 상승 불가 및 동시호가 장난질 신호 언급.</t>
+          <t>기술적 분석 및 외부 요인(정치, 국제 정세)에 따른 상승 및 하락 가능성 혼재.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['특별 배당', '하락 추세', '외인 매수']</t>
+          <t>['기술적 분석', '외국인 수급', '국제 정세']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>214000</v>
+        <v>214750</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-0.70%</t>
+          <t>'-0.35%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="G5" t="n">
-        <v>1795</v>
+        <v>1596</v>
       </c>
       <c r="H5" t="n">
         <v>46.11</v>
@@ -886,7 +886,7 @@
         <v>46.13</v>
       </c>
       <c r="O5" t="n">
-        <v>904437935250</v>
+        <v>985571005000</v>
       </c>
       <c r="P5" t="n">
         <v>374500</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>이재명 및 더불어민주당 리스크, 3분기 영업이익 호재 언급. 기술적 분석 및 나스닥 선물 폭등을 바탕으로 한 긍정적 기대와 함께 시스템 문제 및 폭락 가능성 언급.</t>
+          <t>3분기 영업이익 호재에도 불구하고 정치적 리스크 및 시장 전반의 하락세로 인한 부정적 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['기술적 분석', '영업이익', '시스템 문제']</t>
+          <t>['기술적 분석', '영업이익', '정치 리스크']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58600</v>
+        <v>58900</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-2.01%</t>
+          <t>'-1.51%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>1.49</v>
       </c>
       <c r="E6" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>406</v>
+        <v>425</v>
       </c>
       <c r="H6" t="n">
         <v>40.39</v>
@@ -978,7 +978,7 @@
         <v>38.9</v>
       </c>
       <c r="O6" t="n">
-        <v>124657399650</v>
+        <v>133032125750</v>
       </c>
       <c r="P6" t="n">
         <v>67300</v>
@@ -994,12 +994,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>본격적인 호재 시작 전이며, 1000억대 매수 가능성 언급. 대형 수주 공시 임박 및 외인 공격적 매수세를 근거로 긍정적 전망 제시.</t>
+          <t>대형 수주 공시 임박 기대감과 외인 매수세 유입에 따른 상승 추세 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16450</v>
+        <v>16480</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-2.26%</t>
+          <t>'-2.08%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1044,7 +1044,7 @@
         <v>32</v>
       </c>
       <c r="G7" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H7" t="n">
         <v>27.94</v>
@@ -1070,7 +1070,7 @@
         <v>27.89</v>
       </c>
       <c r="O7" t="n">
-        <v>11301294575</v>
+        <v>12789424685</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>경제 위기 및 30000원 붕괴 가능성 언급. 과거 경영진 비판과 함께 중국 선박 수주 쏠림으로 인한 한국 조선 탈락 뉴스 인용. 투자가 밑 빠진 독에 물 붓기 같다고 평가.</t>
+          <t>수주 부진 및 정치적 요인으로 인한 지속적인 하락세에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['경제 위기', '선박 수주', '밑 빠진 독']</t>
+          <t>['수주 부진', '정치 요인', '하락세']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>57600</v>
+        <v>57900</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-3.03%</t>
+          <t>'-2.53%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F8" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G8" t="n">
-        <v>305</v>
+        <v>344</v>
       </c>
       <c r="H8" t="n">
         <v>22.23</v>
@@ -1162,7 +1162,7 @@
         <v>22.25</v>
       </c>
       <c r="O8" t="n">
-        <v>31044801050</v>
+        <v>33728730800</v>
       </c>
       <c r="P8" t="n">
         <v>139200</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>회사 망한 거 아니냐는 부정적 평가와 함께 두산 묻은 종목 불매 선언. 주식시장 붕괴 및 IMF 가능성 언급. 현재 가격이 저점이라는 반론도 존재.</t>
+          <t>정부 정책 및 시장 전반의 하락세 속에서 회사의 실적 부진 및 주가 하락에 대한 비관론.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['주식시장 붕괴', 'IMF', '저점']</t>
+          <t>['정부 정책', '실적 부진', '주가 하락']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14240</v>
+        <v>14270</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.13%</t>
+          <t>'-2.93%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.14</v>
       </c>
       <c r="E9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G9" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="H9" t="n">
         <v>10.03</v>
@@ -1254,7 +1254,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>11677835580</v>
+        <v>12260587745</v>
       </c>
       <c r="P9" t="n">
         <v>40350</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>이재명 대통령 관련 정치적 언급과 함께 주가 조작, 뱅크런, 마진콜 등 부정적 용어 사용. 건설주 종전/휴전 기대와 실적 나오는 날 공매도 언급.</t>
+          <t>공매도 및 정치적 이슈와 관련된 불확실성 속에 부정적인 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['주가 조작', '뱅크런', '공매도']</t>
+          <t>['공매도', '정치 이슈', '실적']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26900</v>
+        <v>27100</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-5.45%</t>
+          <t>'-4.75%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F10" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G10" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="H10" t="n">
         <v>12.39</v>
@@ -1346,7 +1346,7 @@
         <v>12.34</v>
       </c>
       <c r="O10" t="n">
-        <v>23878287575</v>
+        <v>24649472775</v>
       </c>
       <c r="P10" t="n">
         <v>59300</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>혐오스럽고 만나기 싫은 종목으로 평가. 한국 압박 뉴스 언급 및 방송 후 하락, 거품 논란 제기. 2.7 저점 이탈 시 폭락 우려.</t>
+          <t>거품 논란 및 지속적인 하락세에 대한 비관적인 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['청정에너지', '거품', '폭락']</t>
+          <t>['거품 논란', '하락세', '매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3300</v>
+        <v>3295</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-13.39%</t>
+          <t>'-13.52%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F11" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G11" t="n">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>15492475858</v>
+        <v>16195810347</v>
       </c>
       <c r="P11" t="n">
         <v>7050</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>북한 관련 지정학적 리스크(자주포, 전면전 위기) 언급. 미 선물 폭등 및 외인 매수 가능성 제기. 하락 후 말아올릴 가능성 언급.</t>
+          <t>정치적 긴장 고조 및 시장 상황에 따른 변동성 확대 속 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['지정학적 리스크', '미 선물', '자주포']</t>
+          <t>['정치적 긴장', '변동성', '하락']</t>
         </is>
       </c>
       <c r="X11" t="n">

--- a/data/trending_integrated_20261026_10.xlsx
+++ b/data/trending_integrated_20261026_10.xlsx
@@ -578,13 +578,13 @@
         <v>-0.34</v>
       </c>
       <c r="E2" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G2" t="n">
-        <v>289</v>
+        <v>344</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -610,7 +610,7 @@
         <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>58314729215</v>
+        <v>58382229765</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>글로벌 AI 신약 밸류체인 합류 및 빅파마와의 협력에 따른 급등 및 장기 성장 전망.</t>
+          <t>글로벌 AI 신약 밸류체인 합류 및 빅파마와의 후기 임상 진입 등 구체적인 사업 협력 뉴스 기반으로 한 강력한 긍정적 전망 제시. 공매도 스퀴즈 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI 신약', '빅파마 협력', '급등']</t>
+          <t>['AI', '신약', '임상']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5800</v>
+        <v>5790</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+5.65%</t>
+          <t>'+5.46%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -702,7 +702,7 @@
         <v>2.67</v>
       </c>
       <c r="O3" t="n">
-        <v>22222281295</v>
+        <v>22599936435</v>
       </c>
       <c r="P3" t="n">
         <v>7400</v>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1299000</v>
+        <v>1282000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.72%</t>
+          <t>'+0.39%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -765,10 +765,10 @@
         <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="G4" t="n">
-        <v>1499</v>
+        <v>1523</v>
       </c>
       <c r="H4" t="n">
         <v>48.69</v>
@@ -794,7 +794,7 @@
         <v>48.77</v>
       </c>
       <c r="O4" t="n">
-        <v>1292385439000</v>
+        <v>1370549589000</v>
       </c>
       <c r="P4" t="n">
         <v>2987000</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>기술적 분석 및 외부 요인(정치, 국제 정세)에 따른 상승 및 하락 가능성 혼재.</t>
+          <t>과거 고점 도달에 대한 언급과 함께, 정치적 요인(이재명 지지율, 트럼프) 및 수급 불안정성에 대한 부정적 전망 혼재. 단기적 상승 기대와 하락 우려 공존.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['기술적 분석', '외국인 수급', '국제 정세']</t>
+          <t>['수급', '정치', '하락']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>214750</v>
+        <v>213250</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-0.35%</t>
+          <t>'-1.04%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>461</v>
       </c>
       <c r="G5" t="n">
-        <v>1596</v>
+        <v>1532</v>
       </c>
       <c r="H5" t="n">
         <v>46.11</v>
@@ -886,7 +886,7 @@
         <v>46.13</v>
       </c>
       <c r="O5" t="n">
-        <v>985571005000</v>
+        <v>1032887019250</v>
       </c>
       <c r="P5" t="n">
         <v>374500</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>3분기 영업이익 호재에도 불구하고 정치적 리스크 및 시장 전반의 하락세로 인한 부정적 전망.</t>
+          <t>이재명 및 더불어민주당 관련 정치적 언급이 주를 이루며, 한국 증시 전반에 대한 부정적 전망과 삼성전자 자체에 대한 언급은 미미함. 정치적 요인에 따른 하락 우려 제기.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['기술적 분석', '영업이익', '정치 리스크']</t>
+          <t>['정치', '리스크', '하락']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -946,13 +946,13 @@
         <v>1.49</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G6" t="n">
-        <v>425</v>
+        <v>449</v>
       </c>
       <c r="H6" t="n">
         <v>40.39</v>
@@ -978,7 +978,7 @@
         <v>38.9</v>
       </c>
       <c r="O6" t="n">
-        <v>133032125750</v>
+        <v>135944299250</v>
       </c>
       <c r="P6" t="n">
         <v>67300</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>대형 수주 공시 임박 기대감과 외인 매수세 유입에 따른 상승 추세 전망.</t>
+          <t>대형 수주 공시 임박 가능성 및 외인 매수세 유입에 대한 기대감이 있으나, 일부 공매도에 대한 부정적 언급도 존재. 기술적 분석 및 매수 기회 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['대형 수주', '공시 임박', '외인 매수']</t>
+          <t>['수주', '외인매수', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16480</v>
+        <v>16460</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-2.08%</t>
+          <t>'-2.20%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G7" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H7" t="n">
         <v>27.94</v>
@@ -1070,7 +1070,7 @@
         <v>27.89</v>
       </c>
       <c r="O7" t="n">
-        <v>12789424685</v>
+        <v>13220551370</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>57900</v>
+        <v>57700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.53%</t>
+          <t>'-2.86%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="F8" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G8" t="n">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="H8" t="n">
         <v>22.23</v>
@@ -1162,7 +1162,7 @@
         <v>22.25</v>
       </c>
       <c r="O8" t="n">
-        <v>33728730800</v>
+        <v>35202111950</v>
       </c>
       <c r="P8" t="n">
         <v>139200</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14270</v>
+        <v>14260</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.93%</t>
+          <t>'-2.99%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.14</v>
       </c>
       <c r="E9" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F9" t="n">
         <v>28</v>
       </c>
       <c r="G9" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H9" t="n">
         <v>10.03</v>
@@ -1254,7 +1254,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>12260587745</v>
+        <v>12659731065</v>
       </c>
       <c r="P9" t="n">
         <v>40350</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27100</v>
+        <v>26900</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-4.75%</t>
+          <t>'-5.45%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F10" t="n">
         <v>35</v>
       </c>
       <c r="G10" t="n">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="H10" t="n">
         <v>12.39</v>
@@ -1346,7 +1346,7 @@
         <v>12.34</v>
       </c>
       <c r="O10" t="n">
-        <v>24649472775</v>
+        <v>25589145750</v>
       </c>
       <c r="P10" t="n">
         <v>59300</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>거품 논란 및 지속적인 하락세에 대한 비관적인 전망.</t>
+          <t>연이은 주가 하락에 대한 강한 불만과 부정적 전망이 지배적. 뉴스 언급은 있으나 명확한 근거 제시 없이 종목 자체에 대한 혐오감 표출.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['거품 논란', '하락세', '매도']</t>
+          <t>['하락', '혐오', '전망']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3295</v>
+        <v>3270</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-13.52%</t>
+          <t>'-14.17%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="F11" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G11" t="n">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>16195810347</v>
+        <v>16593524407</v>
       </c>
       <c r="P11" t="n">
         <v>7050</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 긴장 고조 및 시장 상황에 따른 변동성 확대 속 하락 가능성 언급.</t>
+          <t>지정학적 리스크(북한, 이란) 및 국내외 시장 상황에 따른 급락 가능성과 일부 반등에 대한 기대가 혼재. 개인 투자자들의 신용 매매 및 단기 변동성 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['정치적 긴장', '변동성', '하락']</t>
+          <t>['지정학', '급락', '반등']</t>
         </is>
       </c>
       <c r="X11" t="n">

--- a/data/trending_integrated_20261026_10.xlsx
+++ b/data/trending_integrated_20261026_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-0.34</v>
       </c>
       <c r="E2" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F2" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G2" t="n">
-        <v>344</v>
+        <v>382</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -610,7 +610,7 @@
         <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>58382229765</v>
+        <v>58426417285</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>글로벌 AI 신약 밸류체인 합류 및 빅파마와의 후기 임상 진입 등 구체적인 사업 협력 뉴스 기반으로 한 강력한 긍정적 전망 제시. 공매도 스퀴즈 가능성 언급.</t>
+          <t>AI 신약 개발 협력 및 빅파마 파트너십 발표에 따른 주가 급등. 공매도 스퀴즈 기대감 형성.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI', '신약', '임상']</t>
+          <t>['AI 신약', '빅파마', '공매도 스퀴즈']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5790</v>
+        <v>6100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+5.46%</t>
+          <t>'+11.11%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="F3" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G3" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -702,7 +702,7 @@
         <v>2.67</v>
       </c>
       <c r="O3" t="n">
-        <v>22599936435</v>
+        <v>27593995400</v>
       </c>
       <c r="P3" t="n">
         <v>7400</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정치 테마주로서의 실체 없는 기대감에 대한 비판 및 급락 가능성 언급.</t>
+          <t>정치 테마주 관련 언급이 많으며, 특정 정치인의 지지율에 따라 주가 변동 가능성에 대한 기대감이 일부 있으나 명확한 근거는 부족.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['정치 테마주', '실체 없음', '급락']</t>
+          <t>['정치 테마주', '지지율', '기대감']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1282000</v>
+        <v>2135</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+0.39%</t>
+          <t>'+9.83%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.08</v>
+        <v>0.13</v>
       </c>
       <c r="E4" t="n">
-        <v>800</v>
+        <v>42</v>
       </c>
       <c r="F4" t="n">
-        <v>474</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>1523</v>
+        <v>79</v>
       </c>
       <c r="H4" t="n">
-        <v>48.69</v>
+        <v>5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1277000</v>
+        <v>1944</v>
       </c>
       <c r="K4" t="n">
-        <v>1279000</v>
+        <v>2100</v>
       </c>
       <c r="L4" t="n">
-        <v>1315000</v>
+        <v>2325</v>
       </c>
       <c r="M4" t="n">
-        <v>1272000</v>
+        <v>2035</v>
       </c>
       <c r="N4" t="n">
-        <v>48.77</v>
+        <v>4.87</v>
       </c>
       <c r="O4" t="n">
-        <v>1370549589000</v>
+        <v>52119232833</v>
       </c>
       <c r="P4" t="n">
-        <v>2987000</v>
+        <v>4980</v>
       </c>
       <c r="Q4" t="n">
-        <v>501000</v>
+        <v>749</v>
       </c>
       <c r="R4" t="n">
-        <v>19000</v>
+        <v>-78000</v>
       </c>
       <c r="S4" t="n">
-        <v>29000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>과거 고점 도달에 대한 언급과 함께, 정치적 요인(이재명 지지율, 트럼프) 및 수급 불안정성에 대한 부정적 전망 혼재. 단기적 상승 기대와 하락 우려 공존.</t>
+          <t>로봇 섹터 강세 및 신용/단타 투자자 퇴출 언급. 기술적 분석 기반 긍정적 흐름 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['수급', '정치', '하락']</t>
+          <t>['로봇 섹터', '단타', '기술적 분석']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>213250</v>
+        <v>1275000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-1.04%</t>
+          <t>'-0.16%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.02</v>
+        <v>-0.08</v>
       </c>
       <c r="E5" t="n">
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>461</v>
+        <v>482</v>
       </c>
       <c r="G5" t="n">
-        <v>1532</v>
+        <v>1526</v>
       </c>
       <c r="H5" t="n">
-        <v>46.11</v>
+        <v>48.69</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>215500</v>
+        <v>1277000</v>
       </c>
       <c r="K5" t="n">
-        <v>213500</v>
+        <v>1279000</v>
       </c>
       <c r="L5" t="n">
-        <v>216000</v>
+        <v>1315000</v>
       </c>
       <c r="M5" t="n">
-        <v>211500</v>
+        <v>1272000</v>
       </c>
       <c r="N5" t="n">
-        <v>46.13</v>
+        <v>48.77</v>
       </c>
       <c r="O5" t="n">
-        <v>1032887019250</v>
+        <v>1494464188500</v>
       </c>
       <c r="P5" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q5" t="n">
-        <v>94500</v>
+        <v>501000</v>
       </c>
       <c r="R5" t="n">
-        <v>-470000</v>
+        <v>19000</v>
       </c>
       <c r="S5" t="n">
-        <v>56000</v>
+        <v>29000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>이재명 및 더불어민주당 관련 정치적 언급이 주를 이루며, 한국 증시 전반에 대한 부정적 전망과 삼성전자 자체에 대한 언급은 미미함. 정치적 요인에 따른 하락 우려 제기.</t>
+          <t>주가 하락 및 외인 매도세 지속에 대한 우려. 정치적 요인 및 연기금 매도 등 부정적 전망 제기.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['정치', '리스크', '하락']</t>
+          <t>['주가 하락', '외인 매도', '연기금']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,18 +924,18 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58900</v>
+        <v>212250</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -943,19 +943,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.49</v>
+        <v>-0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>102</v>
+        <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>59</v>
+        <v>468</v>
       </c>
       <c r="G6" t="n">
-        <v>449</v>
+        <v>1423</v>
       </c>
       <c r="H6" t="n">
-        <v>40.39</v>
+        <v>46.11</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>59800</v>
+        <v>215500</v>
       </c>
       <c r="K6" t="n">
-        <v>59400</v>
+        <v>213500</v>
       </c>
       <c r="L6" t="n">
-        <v>60200</v>
+        <v>216000</v>
       </c>
       <c r="M6" t="n">
-        <v>57700</v>
+        <v>211500</v>
       </c>
       <c r="N6" t="n">
-        <v>38.9</v>
+        <v>46.13</v>
       </c>
       <c r="O6" t="n">
-        <v>135944299250</v>
+        <v>1102442483500</v>
       </c>
       <c r="P6" t="n">
-        <v>67300</v>
+        <v>374500</v>
       </c>
       <c r="Q6" t="n">
-        <v>23150</v>
+        <v>94500</v>
       </c>
       <c r="R6" t="n">
-        <v>174000</v>
+        <v>-470000</v>
       </c>
       <c r="S6" t="n">
-        <v>-11000</v>
+        <v>56000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>대형 수주 공시 임박 가능성 및 외인 매수세 유입에 대한 기대감이 있으나, 일부 공매도에 대한 부정적 언급도 존재. 기술적 분석 및 매수 기회 언급.</t>
+          <t>정치적 불안정 및 시장 침체 속에서 삼성전자 주가 하락 전망. 그러나 망하지 않는다는 의견도 일부 존재.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['수주', '외인매수', '공매도']</t>
+          <t>['정치', '시장', '하락']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1038,13 +1038,13 @@
         <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G7" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="H7" t="n">
         <v>27.94</v>
@@ -1070,7 +1070,7 @@
         <v>27.89</v>
       </c>
       <c r="O7" t="n">
-        <v>13220551370</v>
+        <v>13845213825</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>수주 부진 및 정치적 요인으로 인한 지속적인 하락세에 대한 부정적 전망.</t>
+          <t>중국 선박 수주 쏠림으로 인한 한국 조선업계 경쟁력 약화 우려. 주가 하락 및 투자 부적절 의견 제기.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['수주 부진', '정치 요인', '하락세']</t>
+          <t>['선박 수주', '경쟁력 약화', '주가 하락']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,79 +1115,79 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>58400</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>'-2.34%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="E8" t="n">
+        <v>105</v>
+      </c>
+      <c r="F8" t="n">
+        <v>60</v>
+      </c>
+      <c r="G8" t="n">
+        <v>470</v>
+      </c>
+      <c r="H8" t="n">
+        <v>40.39</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>59800</v>
+      </c>
+      <c r="K8" t="n">
+        <v>59400</v>
+      </c>
+      <c r="L8" t="n">
+        <v>60200</v>
+      </c>
+      <c r="M8" t="n">
         <v>57700</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>'-2.86%</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="E8" t="n">
-        <v>109</v>
-      </c>
-      <c r="F8" t="n">
-        <v>93</v>
-      </c>
-      <c r="G8" t="n">
-        <v>362</v>
-      </c>
-      <c r="H8" t="n">
-        <v>22.23</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>MarketType.KOSPI</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>59400</v>
-      </c>
-      <c r="K8" t="n">
-        <v>58300</v>
-      </c>
-      <c r="L8" t="n">
-        <v>59100</v>
-      </c>
-      <c r="M8" t="n">
-        <v>57200</v>
-      </c>
       <c r="N8" t="n">
-        <v>22.25</v>
+        <v>38.9</v>
       </c>
       <c r="O8" t="n">
-        <v>35202111950</v>
+        <v>142126146500</v>
       </c>
       <c r="P8" t="n">
-        <v>139200</v>
+        <v>67300</v>
       </c>
       <c r="Q8" t="n">
-        <v>57000</v>
+        <v>23150</v>
       </c>
       <c r="R8" t="n">
-        <v>-1000</v>
+        <v>174000</v>
       </c>
       <c r="S8" t="n">
-        <v>-63000</v>
+        <v>-11000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>정부 정책 및 시장 전반의 하락세 속에서 회사의 실적 부진 및 주가 하락에 대한 비관론.</t>
+          <t>대형 수주 공시 임박 및 외인 매수세 유입에 따른 주가 상승 기대감. 기술적 분석 기반 긍정적 전망 제시.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['정부 정책', '실적 부진', '주가 하락']</t>
+          <t>['수주 공시', '외인 매수', '기술적 분석']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14260</v>
+        <v>57800</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.99%</t>
+          <t>'-2.69%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.14</v>
+        <v>-0.02</v>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>113</v>
       </c>
       <c r="F9" t="n">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="G9" t="n">
-        <v>97</v>
+        <v>395</v>
       </c>
       <c r="H9" t="n">
-        <v>10.03</v>
+        <v>22.23</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14700</v>
+        <v>59400</v>
       </c>
       <c r="K9" t="n">
-        <v>14370</v>
+        <v>58300</v>
       </c>
       <c r="L9" t="n">
-        <v>14770</v>
+        <v>59100</v>
       </c>
       <c r="M9" t="n">
-        <v>14190</v>
+        <v>57200</v>
       </c>
       <c r="N9" t="n">
-        <v>9.890000000000001</v>
+        <v>22.25</v>
       </c>
       <c r="O9" t="n">
-        <v>12659731065</v>
+        <v>37794965200</v>
       </c>
       <c r="P9" t="n">
-        <v>40350</v>
+        <v>139200</v>
       </c>
       <c r="Q9" t="n">
-        <v>3320</v>
+        <v>57000</v>
       </c>
       <c r="R9" t="n">
-        <v>80000</v>
+        <v>-1000</v>
       </c>
       <c r="S9" t="n">
-        <v>-15000</v>
+        <v>-63000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>공매도 및 정치적 이슈와 관련된 불확실성 속에 부정적인 전망.</t>
+          <t>정치적 요인 및 전반적인 증시 침체로 인한 주가 하락 우려. 회사의 실적 및 재무 상태에 대한 부정적 전망 제기.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['공매도', '정치 이슈', '실적']</t>
+          <t>['정치', '증시 침체', '실적']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26900</v>
+        <v>14210</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-5.45%</t>
+          <t>'-3.33%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="E10" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G10" t="n">
-        <v>185</v>
+        <v>107</v>
       </c>
       <c r="H10" t="n">
-        <v>12.39</v>
+        <v>10.03</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>28450</v>
+        <v>14700</v>
       </c>
       <c r="K10" t="n">
-        <v>27900</v>
+        <v>14370</v>
       </c>
       <c r="L10" t="n">
-        <v>28200</v>
+        <v>14770</v>
       </c>
       <c r="M10" t="n">
-        <v>26850</v>
+        <v>14190</v>
       </c>
       <c r="N10" t="n">
-        <v>12.34</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>25589145750</v>
+        <v>13284689530</v>
       </c>
       <c r="P10" t="n">
-        <v>59300</v>
+        <v>40350</v>
       </c>
       <c r="Q10" t="n">
-        <v>22000</v>
+        <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>-134000</v>
+        <v>80000</v>
       </c>
       <c r="S10" t="n">
-        <v>-16000</v>
+        <v>-15000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>연이은 주가 하락에 대한 강한 불만과 부정적 전망이 지배적. 뉴스 언급은 있으나 명확한 근거 제시 없이 종목 자체에 대한 혐오감 표출.</t>
+          <t>주가 조작 및 공매도에 대한 강한 불만 표출. 정치적 이슈와 연관된 부정적 전망 제기.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['하락', '혐오', '전망']</t>
+          <t>['주가 조작', '공매도', '정치']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,97 +1384,189 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>빅텍</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3270</v>
+        <v>26800</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-14.17%</t>
+          <t>'-5.80%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F11" t="n">
-        <v>95</v>
+        <v>37</v>
       </c>
       <c r="G11" t="n">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>12.39</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>3810</v>
+        <v>28450</v>
       </c>
       <c r="K11" t="n">
-        <v>3250</v>
+        <v>27900</v>
       </c>
       <c r="L11" t="n">
-        <v>3555</v>
+        <v>28200</v>
       </c>
       <c r="M11" t="n">
-        <v>3215</v>
+        <v>26750</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>12.34</v>
       </c>
       <c r="O11" t="n">
-        <v>16593524407</v>
+        <v>27300627300</v>
       </c>
       <c r="P11" t="n">
-        <v>7050</v>
+        <v>59300</v>
       </c>
       <c r="Q11" t="n">
-        <v>2500</v>
+        <v>22000</v>
       </c>
       <c r="R11" t="n">
-        <v>173000</v>
+        <v>-134000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-16000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>지정학적 리스크(북한, 이란) 및 국내외 시장 상황에 따른 급락 가능성과 일부 반등에 대한 기대가 혼재. 개인 투자자들의 신용 매매 및 단기 변동성 언급.</t>
+          <t>연이은 주가 하락에 대한 강한 불만과 부정적 전망이 지배적. 뉴스 언급은 있으나 명확한 근거 제시 없이 종목 자체에 대한 혐오감 표출.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['하락', '혐오', '전망']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>009830</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>빅텍</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3245</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>'-14.83%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>155</v>
+      </c>
+      <c r="F12" t="n">
+        <v>96</v>
+      </c>
+      <c r="G12" t="n">
+        <v>242</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>3810</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3250</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3555</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3215</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>17515914485</v>
+      </c>
+      <c r="P12" t="n">
+        <v>7050</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2500</v>
+      </c>
+      <c r="R12" t="n">
+        <v>173000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>정치적 긴장 고조 및 지정학적 리스크에 따른 급락 가능성 경고. 투자 심리 위축.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
         <v>0.2</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>['지정학', '급락', '반등']</t>
-        </is>
-      </c>
-      <c r="X11" t="n">
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['지정학적 리스크', '급락', '투자 심리']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
         <v>5</v>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>065450</t>
         </is>
